--- a/docs/perechen-otchetov/obrazcy/ФО-57.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-57.xlsx
@@ -4483,7 +4483,7 @@
       </c>
       <c r="B42" s="42" t="inlineStr">
         <is>
-          <t>ИТОГО на 01.10.2026 (данные на конец 30.09.2026): 22 заёмщика, 25 кредитов. Основной долг 75 037,500 тыс. сом = ФО-28 = ФО-25 = ФО-24 на конец сентября = ФО-02 «по основной сумме» 67 729,500 + КЗ-25 7 308,000 (в образце ФО-02 его нет). Проценты 2 983,322 = ФО-02 2 970,938 + КЗ-11 0,041 (погашение 05.09.2026 по курсу 87,40 зачло 275,00 USD процентов — на конец 0,22650 тыс. USD = 19,819, как в ФО-53; ФО-02 и ФО-07 до переразбора дают 19,778) + КЗ-25 12,342. Штрафы 541,850 = ФО-02 = ФО-07 на конец. Задолженность всего 78 562,672.</t>
+          <t>ИТОГО на 01.10.2026 (данные на конец 30.09.2026): 22 заёмщика, 25 кредитов. Основной долг 75 037,500 тыс. сом = ФО-28 = ФО-25 = ФО-24 на конец сентября = ФО-02 «по основной сумме» (в том числе КЗ-25 7 308,000). Проценты 2 983,322 = ФО-02 = ФО-07 на конец (в том числе КЗ-11 0,22650 тыс. USD = 19,819 — погашение 05.09.2026 по курсу 87,40 зачло 275,00 USD процентов, как в ФО-53; КЗ-25 121,60 EUR = 12,342). Штрафы 541,850 = ФО-02 = ФО-07 на конец. Задолженность всего 78 562,672.</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="75" customHeight="1">
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" s="41" t="inlineStr">
         <is>
           <t>3.</t>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="B44" s="42" t="inlineStr">
         <is>
-          <t>Группы — по набору на 30.09.2026 (= ФО-24 на конец, ФО-28): 1.1 — 9 заёмщиков, 10 кредитов, основной долг 31 820,500; 1.2 — 7, 7, 13 242,000; 2.1 — 2, 4, 23 375,000; 2.2 — КЗ-05, 2 100,000; 2.3 — КЗ-10, 2 300,000; 3.1 — КЗ-19, 2 200,000; «Нет группы» — КЗ-26 (зарегистрирован 20.08.2026, освоения нет). Колонка «Группа» ФО-01 до переразбора ставит КЗ-05 в 2.1 и КЗ-23 в 2.2 — по набору наоборот.</t>
+          <t>Группы — по набору на 30.09.2026 (= ФО-24 на конец, ФО-28): 1.1 — 9 заёмщиков, 10 кредитов, основной долг 31 820,500; 1.2 — 7, 7, 13 242,000; 2.1 — 2, 4, 23 375,000; 2.2 — КЗ-05, 2 100,000; 2.3 — КЗ-10, 2 300,000; 3.1 — КЗ-19, 2 200,000; «Нет группы» — КЗ-26 (зарегистрирован 20.08.2026, освоения нет).</t>
         </is>
       </c>
     </row>
